--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.66833772804964</v>
+        <v>11.15860488080807</v>
       </c>
       <c r="D2" t="n">
-        <v>57.29349413338672</v>
+        <v>9.310192796675341</v>
       </c>
       <c r="E2" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F2" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.08138677463665</v>
+        <v>8.788225350878456</v>
       </c>
       <c r="D3" t="n">
-        <v>53.35159215284281</v>
+        <v>8.669633724836956</v>
       </c>
       <c r="E3" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F3" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.30576140338008</v>
+        <v>8.662186228049263</v>
       </c>
       <c r="D4" t="n">
-        <v>52.50053683938909</v>
+        <v>8.531337236400727</v>
       </c>
       <c r="E4" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F4" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.97431781622161</v>
+        <v>8.283326645136011</v>
       </c>
       <c r="D5" t="n">
-        <v>48.49416341773453</v>
+        <v>7.880301555381862</v>
       </c>
       <c r="E5" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F5" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.35439007471296</v>
+        <v>7.207588387140857</v>
       </c>
       <c r="D6" t="n">
-        <v>43.68393715979442</v>
+        <v>7.098639788466593</v>
       </c>
       <c r="E6" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F6" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.33127766819991</v>
+        <v>6.878832621082486</v>
       </c>
       <c r="D7" t="n">
-        <v>41.53451083804641</v>
+        <v>6.749358011182542</v>
       </c>
       <c r="E7" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F7" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.72958170627356</v>
+        <v>10.68105702726946</v>
       </c>
       <c r="D8" t="n">
-        <v>42.08622102303793</v>
+        <v>6.839010916243664</v>
       </c>
       <c r="E8" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F8" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.96289000640191</v>
+        <v>5.681469626040311</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61547262794322</v>
+        <v>5.462514302040773</v>
       </c>
       <c r="E9" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F9" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04579214111724</v>
+        <v>4.719941222931552</v>
       </c>
       <c r="D10" t="n">
-        <v>28.51943519976648</v>
+        <v>4.634408219962054</v>
       </c>
       <c r="E10" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F10" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.23167273637091</v>
+        <v>7.350146819660274</v>
       </c>
       <c r="D11" t="n">
-        <v>12.8062484748657</v>
+        <v>2.081015377165676</v>
       </c>
       <c r="E11" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F11" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.7794150033843</v>
+        <v>5.489154938049949</v>
       </c>
       <c r="D12" t="n">
-        <v>3.885828594585572</v>
+        <v>0.6314471466201554</v>
       </c>
       <c r="E12" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F12" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.58413018392503</v>
+        <v>3.832421154887817</v>
       </c>
       <c r="D13" t="n">
-        <v>24.19756854632386</v>
+        <v>3.932104888777628</v>
       </c>
       <c r="E13" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F13" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.9621726429065</v>
+        <v>3.081353054472306</v>
       </c>
       <c r="D14" t="n">
-        <v>8.180904096753476</v>
+        <v>1.32939691572244</v>
       </c>
       <c r="E14" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F14" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.03723235894507</v>
+        <v>3.418550258328574</v>
       </c>
       <c r="D15" t="n">
-        <v>20.24357161768342</v>
+        <v>3.289580387873556</v>
       </c>
       <c r="E15" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F15" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>26.47491071217242</v>
+        <v>4.302172990728018</v>
       </c>
       <c r="D16" t="n">
-        <v>3.102435898925948</v>
+        <v>0.5041458335754665</v>
       </c>
       <c r="E16" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F16" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.02492938724599</v>
+        <v>4.391551025427473</v>
       </c>
       <c r="D17" t="n">
-        <v>4.410935100676853</v>
+        <v>0.7167769538599886</v>
       </c>
       <c r="E17" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F17" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>57.47784493924841</v>
+        <v>9.340149802627867</v>
       </c>
       <c r="D18" t="n">
-        <v>57.99808364143065</v>
+        <v>9.42468859173248</v>
       </c>
       <c r="E18" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F18" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.31345050554902</v>
+        <v>6.713435707151716</v>
       </c>
       <c r="D19" t="n">
-        <v>29.158448262269</v>
+        <v>4.738247842618713</v>
       </c>
       <c r="E19" t="n">
-        <v>14.77033624152403</v>
+        <v>2.400179639247655</v>
       </c>
       <c r="F19" t="n">
-        <v>18.75375682247807</v>
+        <v>3.047485483652685</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
